--- a/output/graficos_nacionales/plot_nacional_m_movinterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_movinterna_a_2019.xlsx
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Movilidad interna (CMI)</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_m_movinterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_movinterna_a_2019.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:22</t>
+    <t xml:space="preserve">2026-07-30 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2185,16 +2185,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_m_movinterna_a_2019.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Movilidad interna (CMI)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -13647,23 +13656,23 @@
         <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -13685,21 +13694,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13708,7 +13717,7 @@
         <v>2019</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_m_movinterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_movinterna_a_2019.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (por 1.000)</t>
   </si>
   <si>
     <t xml:space="preserve">12402</t>
@@ -487,18 +487,18 @@
     <t xml:space="preserve">San Joaquín</t>
   </si>
   <si>
+    <t xml:space="preserve">5602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algarrobo</t>
+  </si>
+  <si>
     <t xml:space="preserve">7110</t>
   </si>
   <si>
     <t xml:space="preserve">San Rafael</t>
   </si>
   <si>
-    <t xml:space="preserve">5602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algarrobo</t>
-  </si>
-  <si>
     <t xml:space="preserve">13131</t>
   </si>
   <si>
@@ -1702,21 +1702,21 @@
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
+    <t xml:space="preserve">9118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toltén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Sauces</t>
+  </si>
+  <si>
     <t xml:space="preserve">14104</t>
   </si>
   <si>
-    <t xml:space="preserve">9118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toltén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Sauces</t>
-  </si>
-  <si>
     <t xml:space="preserve">10107</t>
   </si>
   <si>
@@ -1819,18 +1819,18 @@
     <t xml:space="preserve">Perquenco</t>
   </si>
   <si>
+    <t xml:space="preserve">8309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilleco</t>
+  </si>
+  <si>
     <t xml:space="preserve">9107</t>
   </si>
   <si>
     <t xml:space="preserve">Gorbea</t>
   </si>
   <si>
-    <t xml:space="preserve">8309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilleco</t>
-  </si>
-  <si>
     <t xml:space="preserve">8313</t>
   </si>
   <si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:30</t>
+    <t xml:space="preserve">2026-09-08 10:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2590,9 +2590,9 @@
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="19.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4808,10 +4808,10 @@
         <v>2019</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>156</v>
@@ -4840,10 +4840,10 @@
         <v>2019</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>158</v>
@@ -11112,16 +11112,16 @@
         <v>2019</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>561</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>497</v>
+        <v>562</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>500</v>
@@ -11150,10 +11150,10 @@
         <v>510</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>500</v>
@@ -11176,16 +11176,16 @@
         <v>2019</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>565</v>
+        <v>497</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>500</v>
@@ -11752,10 +11752,10 @@
         <v>2019</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>600</v>
@@ -11784,10 +11784,10 @@
         <v>2019</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>602</v>
@@ -13687,7 +13687,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
